--- a/test_reports/Krinterior_AI_E2E_Test_Report.xlsx
+++ b/test_reports/Krinterior_AI_E2E_Test_Report.xlsx
@@ -9355,7 +9355,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A1:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
